--- a/chosa/20260731_周辺時給調査(九州7店舗).xlsx
+++ b/chosa/20260731_周辺時給調査(九州7店舗).xlsx
@@ -58,7 +58,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -78,11 +78,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -112,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -140,7 +135,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -509,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -964,19 +958,15 @@
       <c r="C11" s="4" t="n">
         <v>1023</v>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>未提供</t>
-        </is>
+      <c r="D11" s="4" t="n">
+        <v>1050</v>
       </c>
       <c r="E11" s="4">
         <f>IF(ISNUMBER(D11),D11-C11,"-")</f>
         <v/>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F11" s="4" t="n">
+        <v>1313</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>130</v>
@@ -986,19 +976,19 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>'宮崎阿波岐原店'!E13</f>
+        <f>'宮崎阿波岐原店'!E14</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>'宮崎阿波岐原店'!E14</f>
+        <f>'宮崎阿波岐原店'!E15</f>
         <v/>
       </c>
       <c r="K11" s="4">
+        <f>'宮崎阿波岐原店'!E17</f>
+        <v/>
+      </c>
+      <c r="L11" s="4">
         <f>'宮崎阿波岐原店'!E16</f>
-        <v/>
-      </c>
-      <c r="L11" s="4">
-        <f>'宮崎阿波岐原店'!E15</f>
         <v/>
       </c>
       <c r="M11" s="4">
@@ -1020,49 +1010,70 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1. 7店舗中6店舗（社内データ提供分すべて）の時給は、県の地域別最低賃金と1円単位で同額です。差は0円です。</t>
+          <t>1. 7店舗中6店舗（陣山・新池・宗像・菊陽・鳥栖真木・佐賀兵庫）の時給は、県の地域別最低賃金と1円単位で同額です。差は0円です。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2. 深夜時給は全店とも 基本時給×1.25 の切り上げで、社内データ内の整合は取れています。</t>
+          <t>2. 宮崎阿波岐原店だけが最低賃金より27円高い1,050円で、7店舗の中で唯一の例外です。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>3. 宮崎阿波岐原店の社内データが未提供です。公開求人には平日1,000円と出ていますが、</t>
+          <t>3. 深夜時給は全店とも 基本時給×1.25 の切り上げで、社内データ内の整合は取れています。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   宮崎県の最低賃金1,023円を下回るため、2025年11月の改定前の旧掲載です。数値として採用していません。</t>
+          <t>4. 全7店舗が周辺相場の中央値を下回っています。差は陣山の-13円から鳥栖真木の-170円までで、</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>4. 公開求人には最低賃金割れの旧掲載が複数ありました（丸亀製麺 鳥栖店980円・佐賀店1,000円・宮崎住吉店1,000円、</t>
+          <t xml:space="preserve">   北九州（陣山・新池）は僅差、佐賀・熊本（鳥栖真木・佐賀兵庫・菊陽）で開きが大きくなっています。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   うどんウエスト 菊陽光の森店900円）。いずれも自動判定で「未確定」に落としています。</t>
+          <t>5. 宮崎阿波岐原店の公開求人は平日1,000円のままで、社内データの1,050円と食い違います。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>5. 周辺相場は公開求人の掲載値であり、実際に支払われている時給ではありません。証明レベルの違いは調査台帳を参照してください。</t>
+          <t xml:space="preserve">   1,000円は宮崎県の最低賃金1,023円を下回るため、2025年11月の改定前の旧掲載です。求人票の更新が必要と思われます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>6. 公開求人には最低賃金割れの旧掲載が複数ありました（丸亀製麺 鳥栖店980円・佐賀店1,000円・宮崎住吉店1,000円、</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   うどんウエスト 菊陽光の森店900円、および上記の自社求人1,000円）。いずれも自動判定で「未確定」に落としています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>7. 周辺相場は公開求人の掲載値であり、実際に支払われている時給ではありません。証明レベルの違いは調査台帳を参照してください。</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1146,7 @@
         </is>
       </c>
       <c r="B5" s="12">
-        <f>COUNTA(調査台帳!$A$6:$A$39)</f>
+        <f>COUNTA(調査台帳!$A$6:$A$40)</f>
         <v/>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -1144,7 +1155,7 @@
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
-      <c r="E5" s="16" t="inlineStr"/>
+      <c r="E5" s="15" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -1153,7 +1164,7 @@
         </is>
       </c>
       <c r="B6" s="12">
-        <f>COUNTIF(調査台帳!$N$6:$N$39,"媒体掲載値")</f>
+        <f>COUNTIF(調査台帳!$N$6:$N$40,"媒体掲載値")</f>
         <v/>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -1162,7 +1173,7 @@
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>これのみ主表に数値表示される</t>
         </is>
@@ -1175,7 +1186,7 @@
         </is>
       </c>
       <c r="B7" s="12">
-        <f>COUNTIF(調査台帳!$N$6:$N$39,"未確定(最低賃金割れ)")</f>
+        <f>COUNTIF(調査台帳!$N$6:$N$40,"未確定(最低賃金割れ)")</f>
         <v/>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1184,7 +1195,7 @@
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>改定前の求人が残っているもの</t>
         </is>
@@ -1197,7 +1208,7 @@
         </is>
       </c>
       <c r="B8" s="12">
-        <f>COUNTIF(調査台帳!$N$6:$N$39,"未確定(店舗非固有)")</f>
+        <f>COUNTIF(調査台帳!$N$6:$N$40,"未確定(店舗非固有)")</f>
         <v/>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -1206,7 +1217,7 @@
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>南柏店サイゼリヤと同型の事故を防ぐ</t>
         </is>
@@ -1219,7 +1230,7 @@
         </is>
       </c>
       <c r="B9" s="12">
-        <f>COUNTIF(調査台帳!$N$6:$N$39,"未確定(施設一般値)")</f>
+        <f>COUNTIF(調査台帳!$N$6:$N$40,"未確定(施設一般値)")</f>
         <v/>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -1228,7 +1239,7 @@
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
-      <c r="E9" s="16" t="inlineStr"/>
+      <c r="E9" s="15" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -1237,7 +1248,7 @@
         </is>
       </c>
       <c r="B10" s="12">
-        <f>COUNTIF(調査台帳!$N$6:$N$39,"未確定(近隣欄からの抽出)")</f>
+        <f>COUNTIF(調査台帳!$N$6:$N$40,"未確定(近隣欄からの抽出)")</f>
         <v/>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -1246,7 +1257,7 @@
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>南柏店の事故そのもののガード</t>
         </is>
@@ -1259,7 +1270,7 @@
         </is>
       </c>
       <c r="B11" s="12">
-        <f>COUNTIF(調査台帳!$N$6:$N$39,"未確定(店舗非特定)")</f>
+        <f>COUNTIF(調査台帳!$N$6:$N$40,"未確定(店舗非特定)")</f>
         <v/>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -1268,7 +1279,7 @@
         </is>
       </c>
       <c r="D11" s="12" t="n"/>
-      <c r="E11" s="16" t="inlineStr"/>
+      <c r="E11" s="15" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -1277,7 +1288,7 @@
         </is>
       </c>
       <c r="B12" s="12">
-        <f>COUNTIF(調査台帳!$N$6:$N$39,"未確定(証拠不足)")</f>
+        <f>COUNTIF(調査台帳!$N$6:$N$40,"未確定(証拠不足)")</f>
         <v/>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -1286,7 +1297,7 @@
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
-      <c r="E12" s="16" t="inlineStr"/>
+      <c r="E12" s="15" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -1295,7 +1306,7 @@
         </is>
       </c>
       <c r="B13" s="12">
-        <f>COUNTIF(調査台帳!$N$6:$N$39,"取得不能")</f>
+        <f>COUNTIF(調査台帳!$N$6:$N$40,"取得不能")</f>
         <v/>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -1304,7 +1315,7 @@
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
-      <c r="E13" s="16" t="inlineStr"/>
+      <c r="E13" s="15" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
@@ -1328,7 +1339,7 @@
       <c r="E14" s="12" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>店舗取り違え・旧掲載 再現テスト</t>
         </is>
@@ -1507,7 +1518,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>最終警告数</t>
         </is>
@@ -1551,7 +1562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P39"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3975,36 +3986,40 @@
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>商業施設内飲食</t>
+          <t>自社(参考)</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>イオンモール宮崎(飲食テナント)</t>
+          <t>資さんうどん 宮崎阿波岐原店の公開求人</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>宮崎県宮崎市新別府町(イオンモール宮崎)</t>
-        </is>
-      </c>
-      <c r="F39" s="9" t="inlineStr"/>
+          <t>宮崎県宮崎市阿波岐原町請田2420</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>12099</t>
+        </is>
+      </c>
       <c r="G39" s="9" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>施設全体で飲食1,200円～・カフェ960円以上</t>
+          <t>平日1,000円～／土日祝1,130円～／深夜 平日1,250円・土日祝1,413円</t>
         </is>
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>施設一般</t>
+          <t>店舗固有求人</t>
         </is>
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>https://am-miyazaki-recruit.jp/job/-/info/list</t>
+          <t>https://sukesan-job.net/jobfind-pc/job/All/12099</t>
         </is>
       </c>
       <c r="K39" s="9" t="n">
@@ -4028,6 +4043,75 @@
         </is>
       </c>
       <c r="P39" s="10" t="inlineStr">
+        <is>
+          <t>★社内データの現行1,050円と食い違う。掲載値1,000円は宮崎県最低賃金1,023円を下回る旧掲載。主表は社内データを正とする</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>宮崎阿波岐原店</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>商業施設内飲食</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>イオンモール宮崎(飲食テナント)</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>宮崎県宮崎市新別府町(イオンモール宮崎)</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr"/>
+      <c r="G40" s="9" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>施設全体で飲食1,200円～・カフェ960円以上</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>施設一般</t>
+        </is>
+      </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>https://am-miyazaki-recruit.jp/job/-/info/list</t>
+        </is>
+      </c>
+      <c r="K40" s="9" t="n">
+        <v>1023</v>
+      </c>
+      <c r="L40" s="9">
+        <f>IF(G40="","-",IF(G40&lt;K40,"割れ(旧掲載疑い)","OK"))</f>
+        <v/>
+      </c>
+      <c r="M40" s="9">
+        <f>IF(AND(D40&lt;&gt;"",E40&lt;&gt;"",F40&lt;&gt;"",G40&lt;&gt;""),"充足","不足")</f>
+        <v/>
+      </c>
+      <c r="N40" s="9">
+        <f>IF(I40="ブランド共通","未確定(店舗非固有)",IF(I40="施設一般","未確定(施設一般値)",IF(I40="近隣求人欄","未確定(近隣欄からの抽出)",IF(I40="店舗非特定","未確定(店舗非特定)",IF(G40="","取得不能",IF(L40="割れ(旧掲載疑い)","未確定(最低賃金割れ)",IF(M40="不足","未確定(証拠不足)","媒体掲載値")))))))</f>
+        <v/>
+      </c>
+      <c r="O40" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="P40" s="10" t="inlineStr">
         <is>
           <t>★施設全体の一般値であり特定テナントの時給ではない</t>
         </is>
@@ -6198,7 +6282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6337,15 +6421,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>宮崎阿波岐原店 現行時給</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>未提供</t>
-        </is>
+      <c r="B7" s="14" t="n">
+        <v>1050</v>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
@@ -6377,15 +6459,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>社内データ未提供。公開求人の1,000円は最低賃金割れの旧掲載のため採用不可</t>
-        </is>
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>深夜時給(22-5時)</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>1313</v>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
@@ -6417,12 +6497,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>土日祝加算</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="14" t="n">
         <v>130</v>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -6455,14 +6535,23 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>土日祝 実質時給</t>
+        </is>
+      </c>
+      <c r="B10" s="14">
+        <f>B7+B9</f>
+        <v/>
+      </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>商業施設内飲食</t>
+          <t>自社(参考)</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>イオンモール宮崎(飲食テナント)</t>
+          <t>資さんうどん 宮崎阿波岐原店の公開求人</t>
         </is>
       </c>
       <c r="F10" s="9">
@@ -6471,7 +6560,7 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>施設全体で飲食1,200円～・カフェ960円以上</t>
+          <t>平日1,000円～／土日祝1,130円～／深夜 平日1,250円・土日祝1,413円</t>
         </is>
       </c>
       <c r="H10" s="9">
@@ -6484,89 +6573,128 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>最低賃金との差</t>
+        </is>
+      </c>
+      <c r="B11" s="14">
+        <f>B7-B4</f>
+        <v/>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>商業施設内飲食</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>イオンモール宮崎(飲食テナント)</t>
+        </is>
+      </c>
+      <c r="F11" s="9">
+        <f>IF(調査台帳!N40="媒体掲載値",調査台帳!G40,"未確定")</f>
+        <v/>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>施設全体で飲食1,200円～・カフェ960円以上</t>
+        </is>
+      </c>
+      <c r="H11" s="9">
+        <f>調査台帳!N40</f>
+        <v/>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>未計測</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>証明レベル</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>取得不能</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>実額確認済み(社内データ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>周辺相場(採用できた値のみ)</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>件数</t>
-        </is>
-      </c>
-      <c r="E13">
-        <f>COUNT(F5:F10)</f>
-        <v/>
       </c>
     </row>
     <row r="14">
       <c r="D14" t="inlineStr">
         <is>
-          <t>最安</t>
+          <t>件数</t>
         </is>
       </c>
       <c r="E14">
-        <f>IF(COUNT(F5:F10)=0,"-",MIN(F5:F10))</f>
+        <f>COUNT(F5:F11)</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="D15" t="inlineStr">
         <is>
-          <t>最高</t>
+          <t>最安</t>
         </is>
       </c>
       <c r="E15">
-        <f>IF(COUNT(F5:F10)=0,"-",MAX(F5:F10))</f>
+        <f>IF(COUNT(F5:F11)=0,"-",MIN(F5:F11))</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="D16" t="inlineStr">
         <is>
-          <t>中央値</t>
+          <t>最高</t>
         </is>
       </c>
       <c r="E16">
-        <f>IF(COUNT(F5:F10)=0,"-",MEDIAN(F5:F10))</f>
+        <f>IF(COUNT(F5:F11)=0,"-",MAX(F5:F11))</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="D17" t="inlineStr">
         <is>
+          <t>中央値</t>
+        </is>
+      </c>
+      <c r="E17">
+        <f>IF(COUNT(F5:F11)=0,"-",MEDIAN(F5:F11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="D18" t="inlineStr">
+        <is>
           <t>自社と中央値の差</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>自社時給が未提供のため算出不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>※「未確定」は数値が無いという意味ではなく、店舗と金額の帰属を確認できていないという意味です。</t>
-        </is>
+      <c r="E18">
+        <f>IF(COUNT(F5:F11)=0,"-",B7-MEDIAN(F5:F11))</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>※「未確定」は数値が無いという意味ではなく、店舗と金額の帰属を確認できていないという意味です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>※距離は未計測です。今回の調査範囲外としています。</t>
         </is>

--- a/chosa/20260731_周辺時給調査(九州7店舗).xlsx
+++ b/chosa/20260731_周辺時給調査(九州7店舗).xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1082,26 +1082,33 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>6. 競合の公開求人にも最低賃金割れの旧掲載が多数ありました。いずれも自動判定で「未確定」に落としています。</t>
+          <t>6. 競合の公開求人には最低賃金割れの旧掲載が21件ありました。うどんウエストは戸畑店1,050円・宗像店1,000円・</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>7. 同一店舗に複数の異なる金額が見つかったもの（ケンタッキー イオンタウン黒崎店、マクドナルド イオン戸畑SC店、</t>
+          <t xml:space="preserve">   菊陽光の森店900円といずれも改定前の掲載で、直接競合であるにもかかわらず現行値を確認できていません。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ケンタッキー 鳥栖店）は、どちらかを自動で選ばず「未確定(情報源の矛盾)」にしています。</t>
+          <t>7. 同一店舗に複数の異なる金額が見つかった4件（ケンタッキー イオンタウン黒崎店、マクドナルド イオン戸畑SC店、</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ケンタッキー 鳥栖店、すき家 57号大津店）は、どちらかを自動で選ばず「未確定(情報源の矛盾)」にしています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>8. 周辺相場は公開求人の掲載値であり、実際に支払われている時給ではありません。実額を確認するには店舗への直接確認が必要です。</t>
         </is>
@@ -1834,122 +1841,140 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>陣山店</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>うどん・そば</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>丸亀製麺(黒崎周辺)</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
-      <c r="G7" s="8" t="n"/>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>店舗別の掲載を取得できず</t>
-        </is>
-      </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>丸亀製麺 八幡本城店</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>北九州市八幡西区本城</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>A10701917138</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>1,000円～／22時以降25%UP</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>対象求人本文</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>https://toridoll-job.com/toridoll02/A10701917138/MDkyujin_d.htm</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>1057</v>
+      </c>
+      <c r="L7" s="7">
+        <f>IF(G7="","-",IF(G7&lt;K7,"割れ(旧掲載疑い)","OK"))</f>
+        <v/>
+      </c>
+      <c r="M7" s="7">
+        <f>IF(AND(D7&lt;&gt;"",E7&lt;&gt;"",F7&lt;&gt;"",G7&lt;&gt;""),"充足","不足")</f>
+        <v/>
+      </c>
+      <c r="N7" s="7">
+        <f>IF(I7="近隣求人欄","未確定(近隣欄からの抽出)",IF(I7="ブランド共通","未確定(店舗非固有)",IF(I7="施設一般","未確定(施設一般値)",IF(I7="店舗非特定","未確定(店舗非特定)",IF(I7="情報源矛盾","未確定(情報源の矛盾)",IF(G7="","取得不能",IF(L7="割れ(旧掲載疑い)","未確定(最低賃金割れ)",IF(M7="不足","未確定(証拠不足)","媒体掲載値"))))))))</f>
+        <v/>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>★福岡県最低賃金1,057円を下回る=旧掲載。八幡西区内の同ブランド店</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>陣山店</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>うどん・そば</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>牧のうどん(八幡西区)</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>求人は福岡市内の店舗のみ(博多バスターミナル1,200円・今宿1,150円・片江1,150円)。北九州市内の店舗を確認できず</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>未取得</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>https://jobs.toridoll.com/marugame</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="n">
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>https://www.baitoru.com/kw/%E7%89%A7%E3%81%AE%E3%81%86%E3%81%A9%E3%82%93%E3%80%80%E6%AD%A3%E7%A4%BE%E5%93%A1%E3%80%80%E6%B1%82%E4%BA%BA/</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="n">
         <v>1057</v>
       </c>
-      <c r="L7" s="8">
-        <f>IF(G7="","-",IF(G7&lt;K7,"割れ(旧掲載疑い)","OK"))</f>
-        <v/>
-      </c>
-      <c r="M7" s="8">
-        <f>IF(AND(D7&lt;&gt;"",E7&lt;&gt;"",F7&lt;&gt;"",G7&lt;&gt;""),"充足","不足")</f>
-        <v/>
-      </c>
-      <c r="N7" s="8">
-        <f>IF(I7="近隣求人欄","未確定(近隣欄からの抽出)",IF(I7="ブランド共通","未確定(店舗非固有)",IF(I7="施設一般","未確定(施設一般値)",IF(I7="店舗非特定","未確定(店舗非特定)",IF(I7="情報源矛盾","未確定(情報源の矛盾)",IF(G7="","取得不能",IF(L7="割れ(旧掲載疑い)","未確定(最低賃金割れ)",IF(M7="不足","未確定(証拠不足)","媒体掲載値"))))))))</f>
-        <v/>
-      </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="L8" s="7">
+        <f>IF(G8="","-",IF(G8&lt;K8,"割れ(旧掲載疑い)","OK"))</f>
+        <v/>
+      </c>
+      <c r="M8" s="7">
+        <f>IF(AND(D8&lt;&gt;"",E8&lt;&gt;"",F8&lt;&gt;"",G8&lt;&gt;""),"充足","不足")</f>
+        <v/>
+      </c>
+      <c r="N8" s="7">
+        <f>IF(I8="近隣求人欄","未確定(近隣欄からの抽出)",IF(I8="ブランド共通","未確定(店舗非固有)",IF(I8="施設一般","未確定(施設一般値)",IF(I8="店舗非特定","未確定(店舗非特定)",IF(I8="情報源矛盾","未確定(情報源の矛盾)",IF(G8="","取得不能",IF(L8="割れ(旧掲載疑い)","未確定(最低賃金割れ)",IF(M8="不足","未確定(証拠不足)","媒体掲載値"))))))))</f>
+        <v/>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="P7" s="8" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>陣山店</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>うどん・そば</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>牧のうどん(八幡西区)</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr"/>
-      <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>店舗別の掲載を取得できず</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>未取得</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>https://jp.indeed.com/</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="n">
-        <v>1057</v>
-      </c>
-      <c r="L8" s="8">
-        <f>IF(G8="","-",IF(G8&lt;K8,"割れ(旧掲載疑い)","OK"))</f>
-        <v/>
-      </c>
-      <c r="M8" s="8">
-        <f>IF(AND(D8&lt;&gt;"",E8&lt;&gt;"",F8&lt;&gt;"",G8&lt;&gt;""),"充足","不足")</f>
-        <v/>
-      </c>
-      <c r="N8" s="8">
-        <f>IF(I8="近隣求人欄","未確定(近隣欄からの抽出)",IF(I8="ブランド共通","未確定(店舗非固有)",IF(I8="施設一般","未確定(施設一般値)",IF(I8="店舗非特定","未確定(店舗非特定)",IF(I8="情報源矛盾","未確定(情報源の矛盾)",IF(G8="","取得不能",IF(L8="割れ(旧掲載疑い)","未確定(最低賃金割れ)",IF(M8="不足","未確定(証拠不足)","媒体掲載値"))))))))</f>
-        <v/>
-      </c>
-      <c r="O8" s="8" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="P8" s="8" t="inlineStr"/>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>★福岡市の値は商圏が違うため使用しない</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
@@ -2797,21 +2822,27 @@
           <t>北九州市戸畑区初音町9-25</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr"/>
-      <c r="G21" s="7" t="n"/>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>job/All/993</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>1050</v>
+      </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>店舗の時給掲載を取得できず</t>
+          <t>1,050～1,313円／22時以降1,313円以上</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>未取得</t>
+          <t>対象求人本文</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>https://west-saiyou.net/</t>
+          <t>https://west-saiyou.net/jobfind-pc/job/All/993</t>
         </is>
       </c>
       <c r="K21" s="7" t="n">
@@ -2836,7 +2867,7 @@
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>★小倉片野店の1,050円は別店舗。使用しない</t>
+          <t>★福岡県最低賃金1,057円を下回る=旧掲載。直接競合のうどん業態</t>
         </is>
       </c>
     </row>
@@ -3786,23 +3817,25 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>store/62</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="n"/>
+          <t>job/All/819</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>1000</v>
+      </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>店舗の時給掲載を取得できず</t>
+          <t>1,000～1,250円／22時以降1,250円以上</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>未取得</t>
+          <t>対象求人本文</t>
         </is>
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>https://www.shop-west.jp/store/62.html</t>
+          <t>https://west-saiyou.net/jobfind-pc/job/All/819</t>
         </is>
       </c>
       <c r="K36" s="7" t="n">
@@ -3827,7 +3860,7 @@
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
-          <t>★佐賀市の1,100円は別県の別店舗。使用しない</t>
+          <t>★福岡県最低賃金1,057円を下回る=旧掲載。直接競合のうどん業態</t>
         </is>
       </c>
     </row>
@@ -3916,23 +3949,25 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>593</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="n"/>
+          <t>job/All/10587</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="n">
+        <v>1070</v>
+      </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>時給の記載を取得できず</t>
+          <t>1,070～1,338円／深夜1,338円／高校生1,060円／早朝(5-9時)+150円</t>
         </is>
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>未取得</t>
+          <t>対象求人本文</t>
         </is>
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>https://jobs.sukiya.jp/shops/593</t>
+          <t>https://work.sukiya.jp/brand-jobfind/job/All/10587</t>
         </is>
       </c>
       <c r="K38" s="8" t="n">
@@ -4100,138 +4135,150 @@
       <c r="P40" s="8" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="n">
+      <c r="A41" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>宗像店</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>ファストフード</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>マクドナルド 宗像サンリブ店</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>福岡県宗像市くりえいと1-5-1</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>40590</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="n"/>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t>時給の記載を取得できず</t>
-        </is>
-      </c>
-      <c r="I41" s="8" t="inlineStr">
-        <is>
-          <t>未取得</t>
-        </is>
-      </c>
-      <c r="J41" s="8" t="inlineStr">
-        <is>
-          <t>https://crewrecruiting.mcdonalds.co.jp/map/40590</t>
-        </is>
-      </c>
-      <c r="K41" s="8" t="n">
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>福岡県宗像市くりえいと1-5-1(赤間駅徒歩11分)</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>job156943548</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>1,000円以上</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>対象求人本文</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>https://www.baitoru.com/kyushu/jlist/fukuoka/kitakyusyushiigai/munakatashi/job156943548/</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="n">
         <v>1057</v>
       </c>
-      <c r="L41" s="8">
+      <c r="L41" s="7">
         <f>IF(G41="","-",IF(G41&lt;K41,"割れ(旧掲載疑い)","OK"))</f>
         <v/>
       </c>
-      <c r="M41" s="8">
+      <c r="M41" s="7">
         <f>IF(AND(D41&lt;&gt;"",E41&lt;&gt;"",F41&lt;&gt;"",G41&lt;&gt;""),"充足","不足")</f>
         <v/>
       </c>
-      <c r="N41" s="8">
+      <c r="N41" s="7">
         <f>IF(I41="近隣求人欄","未確定(近隣欄からの抽出)",IF(I41="ブランド共通","未確定(店舗非固有)",IF(I41="施設一般","未確定(施設一般値)",IF(I41="店舗非特定","未確定(店舗非特定)",IF(I41="情報源矛盾","未確定(情報源の矛盾)",IF(G41="","取得不能",IF(L41="割れ(旧掲載疑い)","未確定(最低賃金割れ)",IF(M41="不足","未確定(証拠不足)","媒体掲載値"))))))))</f>
         <v/>
       </c>
-      <c r="O41" s="8" t="inlineStr">
+      <c r="O41" s="7" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="P41" s="8" t="inlineStr"/>
+      <c r="P41" s="7" t="inlineStr">
+        <is>
+          <t>★福岡県最低賃金1,057円を下回る=旧掲載</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="n">
+      <c r="A42" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>宗像店</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>ファストフード</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>マクドナルド 宗像ミスターマックス店</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>福岡県宗像市</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>40031</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="n"/>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t>時給の記載を取得できず</t>
-        </is>
-      </c>
-      <c r="I42" s="8" t="inlineStr">
-        <is>
-          <t>未取得</t>
-        </is>
-      </c>
-      <c r="J42" s="8" t="inlineStr">
-        <is>
-          <t>https://crewrecruiting.mcdonalds.co.jp/map/40031</t>
-        </is>
-      </c>
-      <c r="K42" s="8" t="n">
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>福岡県宗像市(赤間駅)</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>job60558394</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>992</v>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>992～1,250円／高校生992円～／22-5時25%UP</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>対象求人本文</t>
+        </is>
+      </c>
+      <c r="J42" s="7" t="inlineStr">
+        <is>
+          <t>https://www.baitoru.com/kyushu/jlist/fukuoka/kitakyusyushiigai/munakatashi/job60558394/</t>
+        </is>
+      </c>
+      <c r="K42" s="7" t="n">
         <v>1057</v>
       </c>
-      <c r="L42" s="8">
+      <c r="L42" s="7">
         <f>IF(G42="","-",IF(G42&lt;K42,"割れ(旧掲載疑い)","OK"))</f>
         <v/>
       </c>
-      <c r="M42" s="8">
+      <c r="M42" s="7">
         <f>IF(AND(D42&lt;&gt;"",E42&lt;&gt;"",F42&lt;&gt;"",G42&lt;&gt;""),"充足","不足")</f>
         <v/>
       </c>
-      <c r="N42" s="8">
+      <c r="N42" s="7">
         <f>IF(I42="近隣求人欄","未確定(近隣欄からの抽出)",IF(I42="ブランド共通","未確定(店舗非固有)",IF(I42="施設一般","未確定(施設一般値)",IF(I42="店舗非特定","未確定(店舗非特定)",IF(I42="情報源矛盾","未確定(情報源の矛盾)",IF(G42="","取得不能",IF(L42="割れ(旧掲載疑い)","未確定(最低賃金割れ)",IF(M42="不足","未確定(証拠不足)","媒体掲載値"))))))))</f>
         <v/>
       </c>
-      <c r="O42" s="8" t="inlineStr">
+      <c r="O42" s="7" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="P42" s="8" t="inlineStr"/>
+      <c r="P42" s="7" t="inlineStr">
+        <is>
+          <t>★福岡県最低賃金1,057円を大きく下回る=旧掲載</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n">
@@ -4514,71 +4561,75 @@
       <c r="P46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="n">
+      <c r="A47" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>宗像店</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>商業施設</t>
         </is>
       </c>
-      <c r="D47" s="8" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>サーティワンアイスクリーム くりえいと宗像店</t>
         </is>
       </c>
-      <c r="E47" s="8" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>福岡県宗像市くりえいと</t>
         </is>
       </c>
-      <c r="F47" s="8" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>4149645</t>
         </is>
       </c>
-      <c r="G47" s="8" t="n"/>
-      <c r="H47" s="8" t="inlineStr">
-        <is>
-          <t>時給の記載を取得できず</t>
-        </is>
-      </c>
-      <c r="I47" s="8" t="inlineStr">
+      <c r="G47" s="7" t="n"/>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>確認時点で募集なし(公式求人サイトに掲載なし)</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t>未取得</t>
         </is>
       </c>
-      <c r="J47" s="8" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>https://31ice-job.jp/detail/fukuoka/ct_220/4149645/</t>
         </is>
       </c>
-      <c r="K47" s="8" t="n">
+      <c r="K47" s="7" t="n">
         <v>1057</v>
       </c>
-      <c r="L47" s="8">
+      <c r="L47" s="7">
         <f>IF(G47="","-",IF(G47&lt;K47,"割れ(旧掲載疑い)","OK"))</f>
         <v/>
       </c>
-      <c r="M47" s="8">
+      <c r="M47" s="7">
         <f>IF(AND(D47&lt;&gt;"",E47&lt;&gt;"",F47&lt;&gt;"",G47&lt;&gt;""),"充足","不足")</f>
         <v/>
       </c>
-      <c r="N47" s="8">
+      <c r="N47" s="7">
         <f>IF(I47="近隣求人欄","未確定(近隣欄からの抽出)",IF(I47="ブランド共通","未確定(店舗非固有)",IF(I47="施設一般","未確定(施設一般値)",IF(I47="店舗非特定","未確定(店舗非特定)",IF(I47="情報源矛盾","未確定(情報源の矛盾)",IF(G47="","取得不能",IF(L47="割れ(旧掲載疑い)","未確定(最低賃金割れ)",IF(M47="不足","未確定(証拠不足)","媒体掲載値"))))))))</f>
         <v/>
       </c>
-      <c r="O47" s="8" t="inlineStr">
+      <c r="O47" s="7" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="P47" s="8" t="inlineStr"/>
+      <c r="P47" s="7" t="inlineStr">
+        <is>
+          <t>★他店の1,250～1,310円は別商圏。使用しない</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
@@ -5273,63 +5324,77 @@
       <c r="P57" s="8" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="n">
+      <c r="A58" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>菊陽店</t>
         </is>
       </c>
-      <c r="C58" s="8" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>牛丼・定食</t>
         </is>
       </c>
-      <c r="D58" s="8" t="inlineStr">
-        <is>
-          <t>すき家(菊陽町)</t>
-        </is>
-      </c>
-      <c r="E58" s="8" t="inlineStr"/>
-      <c r="F58" s="8" t="inlineStr"/>
-      <c r="G58" s="8" t="n"/>
-      <c r="H58" s="8" t="inlineStr">
-        <is>
-          <t>菊陽町の店舗別掲載を取得できず</t>
-        </is>
-      </c>
-      <c r="I58" s="8" t="inlineStr">
-        <is>
-          <t>未取得</t>
-        </is>
-      </c>
-      <c r="J58" s="8" t="inlineStr">
-        <is>
-          <t>https://work.sukiya.jp/brand-jobfind/area/All</t>
-        </is>
-      </c>
-      <c r="K58" s="8" t="n">
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>すき家 57号大津店</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>熊本県菊池郡大津町(肥後大津駅徒歩9分)</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>57号大津店</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>媒体A(タウンワーク): 1,200～1,500円　媒体B(バイトル): 950～1,188円</t>
+        </is>
+      </c>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>情報源矛盾</t>
+        </is>
+      </c>
+      <c r="J58" s="7" t="inlineStr">
+        <is>
+          <t>https://townwork.net/job_search/kw/%E7%86%8A%E6%9C%AC%E7%9C%8C+%E8%8F%8A%E6%B1%A0%E9%83%A1+%E5%A4%A7%E6%B4%A5%E7%94%BA/</t>
+        </is>
+      </c>
+      <c r="K58" s="7" t="n">
         <v>1034</v>
       </c>
-      <c r="L58" s="8">
+      <c r="L58" s="7">
         <f>IF(G58="","-",IF(G58&lt;K58,"割れ(旧掲載疑い)","OK"))</f>
         <v/>
       </c>
-      <c r="M58" s="8">
+      <c r="M58" s="7">
         <f>IF(AND(D58&lt;&gt;"",E58&lt;&gt;"",F58&lt;&gt;"",G58&lt;&gt;""),"充足","不足")</f>
         <v/>
       </c>
-      <c r="N58" s="8">
+      <c r="N58" s="7">
         <f>IF(I58="近隣求人欄","未確定(近隣欄からの抽出)",IF(I58="ブランド共通","未確定(店舗非固有)",IF(I58="施設一般","未確定(施設一般値)",IF(I58="店舗非特定","未確定(店舗非特定)",IF(I58="情報源矛盾","未確定(情報源の矛盾)",IF(G58="","取得不能",IF(L58="割れ(旧掲載疑い)","未確定(最低賃金割れ)",IF(M58="不足","未確定(証拠不足)","媒体掲載値"))))))))</f>
         <v/>
       </c>
-      <c r="O58" s="8" t="inlineStr">
+      <c r="O58" s="7" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="P58" s="8" t="inlineStr"/>
+      <c r="P58" s="7" t="inlineStr">
+        <is>
+          <t>★同一店舗に1,200円系と950円系。差が大きく、どちらかを自動で選ばない</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
@@ -5558,18 +5623,20 @@
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>043-06</t>
-        </is>
-      </c>
-      <c r="G62" s="8" t="n"/>
+          <t>043-06 / job-109509242</t>
+        </is>
+      </c>
+      <c r="G62" s="8" t="n">
+        <v>1150</v>
+      </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>時給の記載を取得できず</t>
+          <t>一般1,150円／高校生1,100円／土日祝+50円／22時以降1.25倍</t>
         </is>
       </c>
       <c r="I62" s="8" t="inlineStr">
         <is>
-          <t>未取得</t>
+          <t>対象求人本文</t>
         </is>
       </c>
       <c r="J62" s="8" t="inlineStr">
@@ -5734,71 +5801,77 @@
       <c r="P64" s="8" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="n">
+      <c r="A65" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>鳥栖真木店</t>
         </is>
       </c>
-      <c r="C65" s="8" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>ファストフード</t>
         </is>
       </c>
-      <c r="D65" s="8" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>マクドナルド 鳥栖フレスポ店</t>
         </is>
       </c>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>佐賀県鳥栖市</t>
-        </is>
-      </c>
-      <c r="F65" s="8" t="inlineStr">
-        <is>
-          <t>41505</t>
-        </is>
-      </c>
-      <c r="G65" s="8" t="n"/>
-      <c r="H65" s="8" t="inlineStr">
-        <is>
-          <t>時給の記載を取得できず</t>
-        </is>
-      </c>
-      <c r="I65" s="8" t="inlineStr">
-        <is>
-          <t>未取得</t>
-        </is>
-      </c>
-      <c r="J65" s="8" t="inlineStr">
-        <is>
-          <t>https://crewrecruiting.mcdonalds.co.jp/map/41505</t>
-        </is>
-      </c>
-      <c r="K65" s="8" t="n">
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>佐賀県鳥栖市(鳥栖駅)</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>job156943508</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="n">
+        <v>1020</v>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>1,020円～／勤務10:00-21:30</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>対象求人本文</t>
+        </is>
+      </c>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>https://www.baitoru.com/kyushu/jlist/saga/tosushi/job156943508/</t>
+        </is>
+      </c>
+      <c r="K65" s="7" t="n">
         <v>1030</v>
       </c>
-      <c r="L65" s="8">
+      <c r="L65" s="7">
         <f>IF(G65="","-",IF(G65&lt;K65,"割れ(旧掲載疑い)","OK"))</f>
         <v/>
       </c>
-      <c r="M65" s="8">
+      <c r="M65" s="7">
         <f>IF(AND(D65&lt;&gt;"",E65&lt;&gt;"",F65&lt;&gt;"",G65&lt;&gt;""),"充足","不足")</f>
         <v/>
       </c>
-      <c r="N65" s="8">
+      <c r="N65" s="7">
         <f>IF(I65="近隣求人欄","未確定(近隣欄からの抽出)",IF(I65="ブランド共通","未確定(店舗非固有)",IF(I65="施設一般","未確定(施設一般値)",IF(I65="店舗非特定","未確定(店舗非特定)",IF(I65="情報源矛盾","未確定(情報源の矛盾)",IF(G65="","取得不能",IF(L65="割れ(旧掲載疑い)","未確定(最低賃金割れ)",IF(M65="不足","未確定(証拠不足)","媒体掲載値"))))))))</f>
         <v/>
       </c>
-      <c r="O65" s="8" t="inlineStr">
+      <c r="O65" s="7" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="P65" s="8" t="inlineStr"/>
+      <c r="P65" s="7" t="inlineStr">
+        <is>
+          <t>★佐賀県最低賃金1,030円を下回る=旧掲載</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -6650,23 +6723,25 @@
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>41515</t>
-        </is>
-      </c>
-      <c r="G78" s="8" t="n"/>
+          <t>job156938822</t>
+        </is>
+      </c>
+      <c r="G78" s="8" t="n">
+        <v>1050</v>
+      </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>時給の記載を取得できず</t>
+          <t>1,050円～／高校生22-5時25%UP</t>
         </is>
       </c>
       <c r="I78" s="8" t="inlineStr">
         <is>
-          <t>未取得</t>
+          <t>対象求人本文</t>
         </is>
       </c>
       <c r="J78" s="8" t="inlineStr">
         <is>
-          <t>https://crewrecruiting.mcdonalds.co.jp/map/41515</t>
+          <t>https://www.baitoru.com/kyushu/jlist/saga/sagashi/job156938822/</t>
         </is>
       </c>
       <c r="K78" s="8" t="n">
@@ -6692,71 +6767,77 @@
       <c r="P78" s="8" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="8" t="n">
+      <c r="A79" s="7" t="n">
         <v>74</v>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>佐賀兵庫店</t>
         </is>
       </c>
-      <c r="C79" s="8" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>ファストフード</t>
         </is>
       </c>
-      <c r="D79" s="8" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>ロッテリア モラージュ佐賀店</t>
         </is>
       </c>
-      <c r="E79" s="8" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>佐賀県佐賀市巨勢町(モラージュ佐賀)</t>
         </is>
       </c>
-      <c r="F79" s="8" t="inlineStr">
+      <c r="F79" s="7" t="inlineStr">
         <is>
           <t>1092</t>
         </is>
       </c>
-      <c r="G79" s="8" t="n"/>
-      <c r="H79" s="8" t="inlineStr">
-        <is>
-          <t>時給の記載を取得できず</t>
-        </is>
-      </c>
-      <c r="I79" s="8" t="inlineStr">
-        <is>
-          <t>未取得</t>
-        </is>
-      </c>
-      <c r="J79" s="8" t="inlineStr">
+      <c r="G79" s="7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>1,000円以上</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>対象求人本文</t>
+        </is>
+      </c>
+      <c r="J79" s="7" t="inlineStr">
         <is>
           <t>https://lotteria-arbeit.net/jobfind-pc/job/All/1092</t>
         </is>
       </c>
-      <c r="K79" s="8" t="n">
+      <c r="K79" s="7" t="n">
         <v>1030</v>
       </c>
-      <c r="L79" s="8">
+      <c r="L79" s="7">
         <f>IF(G79="","-",IF(G79&lt;K79,"割れ(旧掲載疑い)","OK"))</f>
         <v/>
       </c>
-      <c r="M79" s="8">
+      <c r="M79" s="7">
         <f>IF(AND(D79&lt;&gt;"",E79&lt;&gt;"",F79&lt;&gt;"",G79&lt;&gt;""),"充足","不足")</f>
         <v/>
       </c>
-      <c r="N79" s="8">
+      <c r="N79" s="7">
         <f>IF(I79="近隣求人欄","未確定(近隣欄からの抽出)",IF(I79="ブランド共通","未確定(店舗非固有)",IF(I79="施設一般","未確定(施設一般値)",IF(I79="店舗非特定","未確定(店舗非特定)",IF(I79="情報源矛盾","未確定(情報源の矛盾)",IF(G79="","取得不能",IF(L79="割れ(旧掲載疑い)","未確定(最低賃金割れ)",IF(M79="不足","未確定(証拠不足)","媒体掲載値"))))))))</f>
         <v/>
       </c>
-      <c r="O79" s="8" t="inlineStr">
+      <c r="O79" s="7" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="P79" s="8" t="inlineStr"/>
+      <c r="P79" s="7" t="inlineStr">
+        <is>
+          <t>★佐賀県最低賃金1,030円を下回る=旧掲載</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
@@ -8136,26 +8217,26 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>丸亀製麺(黒崎周辺)</t>
-        </is>
-      </c>
-      <c r="F6" s="8">
+      <c r="D6" s="7" t="inlineStr"/>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>丸亀製麺 八幡本城店</t>
+        </is>
+      </c>
+      <c r="F6" s="7">
         <f>IF(調査台帳!N7="媒体掲載値",調査台帳!G7,"未確定")</f>
         <v/>
       </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>店舗別の掲載を取得できず</t>
-        </is>
-      </c>
-      <c r="H6" s="8">
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>1,000円～／22時以降25%UP</t>
+        </is>
+      </c>
+      <c r="H6" s="7">
         <f>調査台帳!N7</f>
         <v/>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>未計測</t>
         </is>
@@ -8186,26 +8267,26 @@
       </c>
     </row>
     <row r="7">
-      <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>牧のうどん(八幡西区)</t>
         </is>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="7">
         <f>IF(調査台帳!N8="媒体掲載値",調査台帳!G8,"未確定")</f>
         <v/>
       </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>店舗別の掲載を取得できず</t>
-        </is>
-      </c>
-      <c r="H7" s="8">
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>求人は福岡市内の店舗のみ(博多バスターミナル1,200円・今宿1,150円・片江1,150円)。北九州市内の店舗を確認できず</t>
+        </is>
+      </c>
+      <c r="H7" s="7">
         <f>調査台帳!N8</f>
         <v/>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>未計測</t>
         </is>
@@ -8751,7 +8832,7 @@
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>店舗の時給掲載を取得できず</t>
+          <t>1,050～1,313円／22時以降1,313円以上</t>
         </is>
       </c>
       <c r="H5" s="7">
@@ -9430,7 +9511,7 @@
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>店舗の時給掲載を取得できず</t>
+          <t>1,000～1,250円／22時以降1,250円以上</t>
         </is>
       </c>
       <c r="H5" s="7">
@@ -9442,30 +9523,30 @@
           <t>未計測</t>
         </is>
       </c>
-      <c r="K5" s="8" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>ファストフード</t>
         </is>
       </c>
-      <c r="L5" s="8" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>マクドナルド 宗像ミスターマックス店</t>
         </is>
       </c>
-      <c r="M5" s="8">
+      <c r="M5" s="7">
         <f>IF(調査台帳!N42="媒体掲載値",調査台帳!G42,"未確定")</f>
         <v/>
       </c>
-      <c r="N5" s="8" t="inlineStr">
-        <is>
-          <t>時給の記載を取得できず</t>
-        </is>
-      </c>
-      <c r="O5" s="8">
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>992～1,250円／高校生992円～／22-5時25%UP</t>
+        </is>
+      </c>
+      <c r="O5" s="7">
         <f>調査台帳!N42</f>
         <v/>
       </c>
-      <c r="P5" s="8" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>未計測</t>
         </is>
@@ -9548,7 +9629,7 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>時給の記載を取得できず</t>
+          <t>1,070～1,338円／深夜1,338円／高校生1,060円／早朝(5-9時)+150円</t>
         </is>
       </c>
       <c r="H7" s="8">
@@ -9722,58 +9803,58 @@
       <c r="B10" s="13" t="n">
         <v>130</v>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>ファストフード</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>マクドナルド 宗像サンリブ店</t>
         </is>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="7">
         <f>IF(調査台帳!N41="媒体掲載値",調査台帳!G41,"未確定")</f>
         <v/>
       </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>時給の記載を取得できず</t>
-        </is>
-      </c>
-      <c r="H10" s="8">
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>1,000円以上</t>
+        </is>
+      </c>
+      <c r="H10" s="7">
         <f>調査台帳!N41</f>
         <v/>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>未計測</t>
         </is>
       </c>
-      <c r="K10" s="8" t="inlineStr">
+      <c r="K10" s="7" t="inlineStr">
         <is>
           <t>商業施設</t>
         </is>
       </c>
-      <c r="L10" s="8" t="inlineStr">
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>サーティワンアイスクリーム くりえいと宗像店</t>
         </is>
       </c>
-      <c r="M10" s="8">
+      <c r="M10" s="7">
         <f>IF(調査台帳!N47="媒体掲載値",調査台帳!G47,"未確定")</f>
         <v/>
       </c>
-      <c r="N10" s="8" t="inlineStr">
-        <is>
-          <t>時給の記載を取得できず</t>
-        </is>
-      </c>
-      <c r="O10" s="8">
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>確認時点で募集なし(公式求人サイトに掲載なし)</t>
+        </is>
+      </c>
+      <c r="O10" s="7">
         <f>調査台帳!N47</f>
         <v/>
       </c>
-      <c r="P10" s="8" t="inlineStr">
+      <c r="P10" s="7" t="inlineStr">
         <is>
           <t>未計測</t>
         </is>
@@ -10287,30 +10368,30 @@
           <t>未計測</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K9" s="7" t="inlineStr">
         <is>
           <t>牛丼・定食</t>
         </is>
       </c>
-      <c r="L9" s="8" t="inlineStr">
-        <is>
-          <t>すき家(菊陽町)</t>
-        </is>
-      </c>
-      <c r="M9" s="8">
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>すき家 57号大津店</t>
+        </is>
+      </c>
+      <c r="M9" s="7">
         <f>IF(調査台帳!N58="媒体掲載値",調査台帳!G58,"未確定")</f>
         <v/>
       </c>
-      <c r="N9" s="8" t="inlineStr">
-        <is>
-          <t>菊陽町の店舗別掲載を取得できず</t>
-        </is>
-      </c>
-      <c r="O9" s="8">
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>媒体A(タウンワーク): 1,200～1,500円　媒体B(バイトル): 950～1,188円</t>
+        </is>
+      </c>
+      <c r="O9" s="7">
         <f>調査台帳!N58</f>
         <v/>
       </c>
-      <c r="P9" s="8" t="inlineStr">
+      <c r="P9" s="7" t="inlineStr">
         <is>
           <t>未計測</t>
         </is>
@@ -10750,7 +10831,7 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>時給の記載を取得できず</t>
+          <t>一般1,150円／高校生1,100円／土日祝+50円／22時以降1.25倍</t>
         </is>
       </c>
       <c r="H7" s="8">
@@ -10924,30 +11005,30 @@
       <c r="B10" s="13" t="n">
         <v>130</v>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>ファストフード</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>マクドナルド 鳥栖フレスポ店</t>
         </is>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="7">
         <f>IF(調査台帳!N65="媒体掲載値",調査台帳!G65,"未確定")</f>
         <v/>
       </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>時給の記載を取得できず</t>
-        </is>
-      </c>
-      <c r="H10" s="8">
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>1,020円～／勤務10:00-21:30</t>
+        </is>
+      </c>
+      <c r="H10" s="7">
         <f>調査台帳!N65</f>
         <v/>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>未計測</t>
         </is>
@@ -11231,7 +11312,7 @@
       </c>
       <c r="N5" s="8" t="inlineStr">
         <is>
-          <t>時給の記載を取得できず</t>
+          <t>1,050円～／高校生22-5時25%UP</t>
         </is>
       </c>
       <c r="O5" s="8">
@@ -11279,26 +11360,26 @@
           <t>未計測</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="8" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr"/>
+      <c r="L6" s="7" t="inlineStr">
         <is>
           <t>ロッテリア モラージュ佐賀店</t>
         </is>
       </c>
-      <c r="M6" s="8">
+      <c r="M6" s="7">
         <f>IF(調査台帳!N79="媒体掲載値",調査台帳!G79,"未確定")</f>
         <v/>
       </c>
-      <c r="N6" s="8" t="inlineStr">
-        <is>
-          <t>時給の記載を取得できず</t>
-        </is>
-      </c>
-      <c r="O6" s="8">
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>1,000円以上</t>
+        </is>
+      </c>
+      <c r="O6" s="7">
         <f>調査台帳!N79</f>
         <v/>
       </c>
-      <c r="P6" s="8" t="inlineStr">
+      <c r="P6" s="7" t="inlineStr">
         <is>
           <t>未計測</t>
         </is>
